--- a/data/B25BLOG_TIN12.xlsx
+++ b/data/B25BLOG_TIN12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CDF987-A2F3-41D1-A379-AA6F8CD832AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB7838E-0B27-4E9E-8B9B-61223C771444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_HUONG_DAN" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="222">
   <si>
     <t>BÀI 25 – BLOG CÁ NHÂN (BÀI TẬP NHÓM) – Tin học 12</t>
   </si>
@@ -698,6 +698,14 @@
 Nhận xét: ...
 Trạng thái: ĐÃ CHẤM | KHÔNG MỞ ĐƯỢC LINK
 </t>
+  </si>
+  <si>
+    <t>QUY TRÌNH CHẤM THỰC TẾ (GitHub Pages không tự gọi AI khi nộp):
+1) HS nộp link → dòng KetQua Bài=B25, Điểm=0, Họ tên=đủ thành viên nhóm, Bài làm=BLOG|link|thành viên
+2) GV mở Chatbox AI (Gemini/ChatGPT) → dán Prompt + Link + danh sách thành viên
+3) AI trả Tổng + Nhận xét → GV ghi vào cột Điểm và (tuỳ chọn) cột ghi chú trên Sheet
+4) HS F5 trang Bài 25 → bảng đọc điểm từ Sheet (action=list) và hiện Tổng + Đã chấm
+Muốn CHẤM TỰ ĐỘNG 100% khi nộp: cần API key (Gemini) trong Apps Script doPost → gọi model → ghi điểm. Không làm được chỉ bằng HTML tĩnh.</t>
   </si>
   <si>
     <t>LOCK</t>
@@ -799,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -821,6 +829,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3183,10 +3194,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3205,10 +3216,10 @@
         <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="E4" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3216,10 +3227,10 @@
         <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3383,7 +3394,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -3399,6 +3410,11 @@
         <v>219</v>
       </c>
     </row>
+    <row r="5" spans="1:1" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
